--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_29-12-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_29-12-2025.xlsx
@@ -461,62 +461,62 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>InsulationUK</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Online Insulation Sales</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Insulation Hub</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Insulation Online</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Planet Insulation</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Insulation Shop</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Insulation Bee</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Trade Insulations</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>Materials Market</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Trade Insulations</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Insulation Wholesale</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Insulation Hub</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>InsulationUK</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Online Insulation Sales</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Building Materials</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Insulation Online</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Planet Insulation</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Insulation Shop</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Insulation Bee</t>
-        </is>
-      </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>DIY Building supplies</t>
+          <t>DIY Building Supplies</t>
         </is>
       </c>
     </row>
@@ -553,57 +553,57 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>£9.60</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>£9.70</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>£11.17</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>£15.52</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>£9.77</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>£20.73</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>£10.25</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>£23.87</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>£9.69</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>£9.69</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>£9.47</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>£11.17</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>£9.60</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>£9.70</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>£15.52</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>£9.77</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>£20.73</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>£10.25</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>£23.87</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -645,57 +645,57 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>£11.54</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>£11.09</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>£12.83</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>£18.20</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>£11.89</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>£23.92</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>£11.86</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>£27.67</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>£11.09</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>£11.1</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>£11.09</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>£11.40</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>£12.83</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>£11.54</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>£11.09</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>£18.20</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>£11.89</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>£23.92</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>£11.86</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>£27.67</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -737,57 +737,57 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>£13.80</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>£14.01</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>£16.46</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>£21.50</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>£14.44</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>£28.00</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>£14.59</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>£29.74</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>£14.01</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>£14.0</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>£14.01</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>£13.87</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>£16.46</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>£13.80</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>£14.01</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>£21.50</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>£14.44</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>£28.00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>£14.59</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>£29.74</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -829,57 +829,57 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>£14.98</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>£14.55</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>£16.75</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>£22.89</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>£15.4</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>£30.19</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>£16.21</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>£32.42</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>£14.55</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>£14.55</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>£16.75</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>£14.98</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>£14.55</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>£22.89</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>£15.4</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>£30.19</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>£16.21</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>£32.42</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -921,57 +921,57 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>£17.88</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>£18.15</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>£21.46</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>£26.90</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>£19.19</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>£35.91</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>£19.42</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>£39.12</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>£18.15</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>£18.16</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>£18.15</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>£18.04</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>£21.46</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>£17.88</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>£18.15</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>£26.90</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>£19.19</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>£35.91</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>£19.42</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>£39.12</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1013,57 +1013,57 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>£19.95</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>£20.24</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>£23.15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>£33.11</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>£21.62</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>£43.61</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>£21.03</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>£46.64</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>£20.30</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>£20.24</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>£20.13</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>£23.15</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>£19.95</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>£20.24</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>£33.11</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>£21.62</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>£43.61</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>£21.03</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>£46.64</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1105,57 +1105,57 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>£19.98</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>£20.30</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>£23.50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>£34.47</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>£20.97</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>£45.09</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>£21.39</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>£46.55</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>£20.30</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>£20.13</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>£20.30</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>£20.16</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>£23.50</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>£19.98</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>£20.30</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>£34.47</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>£20.97</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>£45.09</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>£21.39</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>£46.55</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1197,57 +1197,57 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>£23.68</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>£23.38</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>£26.79</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>£35.94</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>£23.83</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>£48.08</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>£23.54</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>£51.7</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>£23.38</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>£23.35</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>£23.38</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>£23.32</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>£26.79</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>£23.68</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>£23.38</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>£35.94</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>£23.83</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>£48.08</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>£23.54</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>£51.7</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1289,57 +1289,57 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>£25.22</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>£25.40</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>£29.33</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>£39.16</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>£26.35</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>£53.13</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>£25.87</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>£57.31</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>£25.45</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>£25.4</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>£25.45</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>£24.95</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>£29.33</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>£25.22</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>£25.40</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>£39.16</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>£26.35</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>£53.13</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>£25.87</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>£57.31</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1381,57 +1381,57 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>£24.75</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>£25.00</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>£27.29</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>£41.36</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>£26.35</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>£54.41</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>£27.02</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>£49.55</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>£25.10</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>£25.1</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>£25.10</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>£24.38</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>£27.29</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>£24.75</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>£25.00</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>£41.36</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>£26.35</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>£54.41</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>£27.02</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>£49.55</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1473,57 +1473,57 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>£31.87</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>£41.79</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>£50.37</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>£31.88</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>£50.96</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>POA</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
           <t>£32.15</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>£32.15</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>£30.69</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>£41.79</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>£31.87</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>£50.37</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>£31.88</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>£50.96</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>POA</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1565,57 +1565,57 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>£30.10</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>£30.40</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>£35.08</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>£50.30</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>£32.98</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>£66.89</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>£32.54</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>£74.18</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>£30.45</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
           <t>£30.4</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>£30.45</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>£30.27</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>£35.08</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>£30.10</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>£30.40</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>£50.30</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>£32.98</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>£66.89</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>£32.54</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>£74.18</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1657,57 +1657,57 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>£37.14</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>£37.40</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>£46.74</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>£58.68</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>£37.39</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>£73.80</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>£37.14</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>£81.55</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>£37.40</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
           <t>£38.0</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>£37.40</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>£37.00</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>£46.74</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>£37.14</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>£37.40</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>£58.68</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>£37.39</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>£73.80</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>£37.14</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>£81.55</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1749,57 +1749,57 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>£37.25</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>£37.79</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>£47.29</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>£62.87</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>£40.35</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>£78.85</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>£40.25</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>£86.21</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>£38.50</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
           <t>£37.94</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>£38.50</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>£37.59</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>£47.29</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>£37.25</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>£37.79</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>£62.87</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>£40.35</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>£78.85</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>£40.25</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>£86.21</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1841,57 +1841,57 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>£37.10</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>£37.32</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>£43.58</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>£59.49</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>£39.6</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>£82.06</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>£39.47</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>£89.87</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>£37.50</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>£37.32</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>£36.83</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>£43.58</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>£37.10</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>£37.32</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>£59.49</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>£39.6</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>£82.06</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>£39.47</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>£89.87</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1933,57 +1933,57 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>£690.66</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>£857.88</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>£634.53</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>£959.7</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>POA</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>£719.88</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
           <t>£877.92</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>£719.88</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Price Not Found</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>£857.88</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>£690.66</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>£634.53</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>£959.7</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>POA</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2025,57 +2025,57 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>£1407.24</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>£867.05</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>£1029.48</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>£1,141.98</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>£853.62</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>£1164.06</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>POA</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>£935.88</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
           <t>£960.0</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>£935.88</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Price Not Found</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>£1029.48</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>£1407.24</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>£867.05</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>£1,141.98</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>£853.62</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>£1164.06</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>POA</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2117,57 +2117,57 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>£26.63</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>£25.50</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>£37.39</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>£34.56</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>£36.95</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>£68.31</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>£48.24</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>£51.2</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>£26.99</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
           <t>£28.12</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>£26.99</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>£26.90</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>£37.39</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>£26.63</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>£25.50</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>£34.56</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>£36.95</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>£68.31</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>£48.24</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>£51.2</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2209,57 +2209,57 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>£32.37</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>£31.05</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>£47.29</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>£41.09</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>£44.24</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>£79.12</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>£58.53</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>£59.2</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>£32.99</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
           <t>£33.87</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>£32.99</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>£31.65</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>£47.29</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>£32.37</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>£31.05</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>£41.09</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>£44.24</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>£79.12</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>£58.53</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>£59.2</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2301,57 +2301,57 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t>£35.65</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>£34.10</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>£49.49</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>£48.75</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>£52.32</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>£87.37</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>£66.08</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>£79.58</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>£35.99</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
           <t>£36.81</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>£35.99</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>£35.60</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>£49.49</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>£35.65</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>£34.10</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>£48.75</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>£52.32</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>£87.37</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>£66.08</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>£79.58</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2393,57 +2393,57 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>£40.59</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>£38.80</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>£54.99</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>£53.63</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>£55.49</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>£92.82</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>£68.87</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>£70.18</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>£40.99</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
           <t>£41.98</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>£40.99</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>£40.48</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>£54.99</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>£40.59</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>£38.80</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>£53.63</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>£55.49</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>£92.82</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>£68.87</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>£70.18</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2485,57 +2485,57 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>£43.55</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>£78.54</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>£65.53</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>£41.25</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>£68.43</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>£65.48</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>POA</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>£43.79</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
           <t>£49.6</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>£43.79</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>£42.88</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>£78.54</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>£43.55</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>£65.53</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>£41.25</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>£68.43</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>£65.48</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>POA</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2577,57 +2577,57 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>£47.03</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>£85.44</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>£66.65</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>£39.38</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>£71.62</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>£63.59</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>POA</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>£43.25</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
           <t>£48.04</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>£43.25</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>£42.88</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>£85.44</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>£47.03</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>£66.65</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>£39.38</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>£71.62</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>£63.59</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>POA</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2674,52 +2674,52 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>£1191.68</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>£1439.04</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>POA</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
           <t>£924.00</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>N/L</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>N/L</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>£1191.68</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>£1439.04</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>POA</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2761,57 +2761,57 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>£43.05</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>£81.9</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>£66.18</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>£40.53</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>£72.21</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>£62.02</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>POA</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>£42.80</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
           <t>£46.5</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>£42.80</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>£42.88</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>£81.9</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>£43.05</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>£66.18</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>£40.53</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>£72.21</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>£62.02</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>POA</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2853,57 +2853,57 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>£1107.2</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>£1172.16</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>£1057.71</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>£1948.16</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>£1588.8</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>£1152.0</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
           <t>£1248.0</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>£1152.0</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>£1117.12</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>£1172.16</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>£1107.2</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>£1057.71</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>£1948.16</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>£1588.8</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>N/L</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2945,57 +2945,57 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>£1242.08</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>£1407.2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>£1126.15</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>£2157.92</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>£1700.0</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>£1280.0</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
           <t>£1328.0</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>£1280.0</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>£1252.8</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>£1407.2</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>£1242.08</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>£1126.15</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>£2157.92</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>£1700.0</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>N/L</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3037,52 +3037,52 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>£1177.28</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>£1336.96</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>£1096.66</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>£1804.16</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
           <t>£1280.0</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>£1280.0</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>£1336.96</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>£1177.28</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>£1096.66</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>£1804.16</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
